--- a/docs/NIDP_FEEDS/Master_Data_Feed_Template.xlsx
+++ b/docs/NIDP_FEEDS/Master_Data_Feed_Template.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Instructions" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Feed Inventory" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Scoring &amp; Derived Tables" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Tasks" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instructions" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Feed Inventory" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Scoring &amp; Derived Tables" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tasks" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Tasks'!$A$4:$M$29</definedName>
@@ -854,7 +854,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:AB40"/>
+  <dimension ref="A1:AB45"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="18" customWidth="1" style="9" min="1" max="2"/>
@@ -2384,7 +2384,7 @@
       </c>
       <c r="N12" s="17" t="inlineStr">
         <is>
-          <t>NSE (primary XBRL); company IR pages (fallback scrape + LLM extract)</t>
+          <t>NSE corporate-announcements API (primary XBRL _WEB.xml); company IR pages via company_ir_urls table (secondary scrape); NSE XBRL comparator API (tertiary JSON)</t>
         </is>
       </c>
       <c r="O12" s="17" t="inlineStr">
@@ -2419,7 +2419,12 @@
       </c>
       <c r="U12" s="17" t="inlineStr">
         <is>
-          <t>GET list → per filing: try company IR page first (scrape + Claude LLM extraction) → fallback to NSE XBRL comparator → parse XBRL namespace-agnostic by local-name → emit standalone + consolidated rows if both present → scale ₹ to crores → COALESCE upsert.</t>
+          <t>3-strategy pipeline per company:
+1) NSE Integrated XBRL filing (_WEB.xml via corporate-announcements API) — zero LLM tokens, reads IndAS/IGAAP contextRef='OneD' P&amp;L + 'OneI' balance sheet
+2) Company IR page (ir_url from company_ir_urls) — scrape HTML/PDF, extract text (pdfminer for PDFs), pass to LLM if not XML
+3) NSE XBRL comparator API (JSON) — parse JSON directly, LLM fallback
+LLM backend: OPENAI_API_KEY → gpt-4o-mini; else ANTHROPIC_API_KEY → claude-haiku-4-5
+period_end inferred from event_date if LLM returns null</t>
         </is>
       </c>
       <c r="V12" s="17" t="inlineStr">
@@ -2454,7 +2459,9 @@
       </c>
       <c r="AB12" s="17" t="inlineStr">
         <is>
-          <t>15d: 19 OK / 0 FAILED. FLAG: LLM fallback (Claude Haiku) means quiet API-key dependency; failure mode if ANTHROPIC_API_KEY rotates without redeploy.</t>
+          <t>Updated 2026-05-26: 3-strategy pipeline with NSE Integrated XBRL as primary (no LLM).
+OpenAI gpt-4o-mini added as primary LLM backend (Anthropic Haiku fallback).
+15d: 19 OK / 0 FAILED. FLAG: LLM fallback means quiet API-key dependency; OPENAI_API_KEY must be set in nidp.env. Source run_id written per upsert for dedup tracing.</t>
         </is>
       </c>
     </row>
@@ -6431,6 +6438,566 @@
       <c r="AB40" s="19" t="inlineStr">
         <is>
           <t>15d: 4 OK / 141 FAILED. **CRITICAL**: failure is NotFound 404 on gs://nidp-raw-niveshdataintelligence/portfolio/holdings/2025-07-31/holdings.jsonl. The upstream Nivesh portfolio_gcs_export is either NOT writing files OR writing to a different bucket/path. 141 failures = run scheduled but file never lands. Investigate Nivesh app's export job.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Feed 38</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>V3_SCORES_ENGINE</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>v3_scores_engine</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>PROD</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Linux cron (/etc/cron.d/nidp)</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>23:55 IST (Mon-Fri)</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Daily (trading days)</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>55 23 * * 1-5  (IST)</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>Time-based</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>Computes and persists V3 composite Quality + Health scores for every MF scheme and NSE stock. Writes nightly snapshot rows to nidp.v3_mf_scores_daily and nidp.v3_stock_scores_daily.</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>Derived scoring: Quality score (0-100), Health score (0-100) per MF/stock. Served by /v1/{mf,stocks}/scores/*.</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>Internal derived</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>TimescaleDB: nidp.mf_derived_analytics, nidp.stock_features_daily, nidp.technical_indicators</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>nidp.v3_mf_scores_daily  •  nidp.v3_stock_scores_daily</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>Postgres 16 + TimescaleDB (nidp-postgres, db: nidp)</t>
+        </is>
+      </c>
+      <c r="R41" t="inlineStr">
+        <is>
+          <t>Insert with date partition; idempotent via ON CONFLICT (date, isin/symbol)</t>
+        </is>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>backend/nidp/services/v3_scores_engine/</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>mf_derived_refresh (23:50)  •  fundamental_engine (23:05)  •  technical_indicator_engine (22:35)</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Nivesh portfolio health scoring  •  /api/insights/v3-portfolio  •  intelligence_layer</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>~2-5 min</t>
+        </is>
+      </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>Grafana NIDP Feed Schedule and Status</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>Idempotent. Manual: sudo -u nidp run_service.sh v3_scores_engine</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Feed 39</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>ANALYTICS_REFRESH</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>analytics_refresh</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>PROD</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Linux cron (/etc/cron.d/nidp)</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>00:10 IST (Tue-Sat, i.e. after Mon-Fri trading sessions)</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Daily (trading days + 1)</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>10 0 * * 2-6  (IST)</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>Time-based</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>Populates analytics.stock_card + analytics.sector_snapshot and refreshes 4 materialized views: mv_top_momentum, mv_delivery_surge, mv_sector_heatmap, mv_fund_category_top10.</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>Derived analytics: momentum, delivery surge, sector heatmap, fund category rankings</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>Internal derived</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>TimescaleDB: nidp.bhavcopy, nidp.delivery, nidp.stock_features_daily, nidp.v3_stock_scores_daily</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>analytics.stock_card  •  analytics.sector_snapshot  •  analytics.mv_top_momentum  •  analytics.mv_delivery_surge  •  analytics.mv_sector_heatmap  •  analytics.mv_fund_category_top10</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>Postgres 16 + TimescaleDB (nidp-postgres, db: nidp)</t>
+        </is>
+      </c>
+      <c r="R42" t="inlineStr">
+        <is>
+          <t>Upsert + REFRESH MATERIALIZED VIEW CONCURRENTLY</t>
+        </is>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>backend/nidp/services/analytics_refresh/</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>v3_scores_engine (23:55)  •  snapshot_builder (22:00)  •  technical_indicator_engine (22:35)</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>DaaS API analytics endpoints  •  market intelligence feeds</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>~3-8 min</t>
+        </is>
+      </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>Grafana NIDP Feed Schedule and Status</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>Idempotent REFRESH + upsert. Manual: sudo -u nidp run_service.sh analytics_refresh</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Feed 40</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>PORTFOLIO_TRANSACTIONS_SYNC</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>portfolio_transactions_sync</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>PROD</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Linux cron (/etc/cron.d/nidp)</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>23:10 IST (Mon-Fri)</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Daily (trading days)</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>10 23 * * 1-5  (IST)</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>Time-based</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>Reads per-user transaction JSONL exports from GCS and upserts into portfolio.user_transactions_snapshot. Runs after portfolio_holdings_sync to ensure client_master rows exist.</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>Per-user transactions: buy/sell/switch/dividend history. PII.</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>Internal (per-user PII)</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>GCS landing zone: gs://{NIDP_GCS_BUCKET}/portfolio/transactions/{date}/transactions.jsonl</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>portfolio.user_transactions_snapshot</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>Postgres 16 + TimescaleDB (nidp-postgres, db: nidp)</t>
+        </is>
+      </c>
+      <c r="R43" t="inlineStr">
+        <is>
+          <t>Upsert with dedup hash</t>
+        </is>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>backend/nidp/services/portfolio_transactions_sync/</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>portfolio_holdings_sync (23:00) — must succeed first</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>portfolio_intelligence_sync  •  tax engine  •  performance analytics</t>
+        </is>
+      </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>Grafana NIDP Feed Schedule and Status</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>Idempotent. Manual: sudo -u nidp run_service.sh portfolio_transactions_sync</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>BLOCKED by portfolio_holdings_sync GCS 404 failure. Fix GCS export in Nivesh app first.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Feed 41</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>PORTFOLIO_GOALS_SYNC</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>portfolio_goals_sync</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>PROD</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>Linux cron (/etc/cron.d/nidp)</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>23:15 IST (Mon-Fri)</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Daily (trading days)</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>15 23 * * 1-5  (IST)</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>Time-based</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>Syncs per-user goal definitions from Nivesh PG (user_goals) to NIDP so the intelligence_layer can evaluate goal alignment and compute on_track_pct.</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>Per-user goals: target amount, horizon, current corpus, SIP, on-track %. PII.</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>Internal (per-user PII)</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>Nivesh Postgres: user_goals table (GCS or direct PG bridge)</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>portfolio.user_goals_snapshot</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>Postgres 16 + TimescaleDB (nidp-postgres, db: nidp)</t>
+        </is>
+      </c>
+      <c r="R44" t="inlineStr">
+        <is>
+          <t>Upsert</t>
+        </is>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>backend/nidp/services/portfolio_goals_sync/</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>portfolio_holdings_sync (23:00)  •  portfolio_transactions_sync (23:10)</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>intelligence_layer (23:20)  •  portfolio_intelligence_sync (23:30)  •  Goal Alignment Engine</t>
+        </is>
+      </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>Grafana NIDP Feed Schedule and Status</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>Idempotent. Manual: sudo -u nidp run_service.sh portfolio_goals_sync</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Feed 42</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>AMC_URLS_DRIFT_CHECK</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>amc_urls_drift_check</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>PROD</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Linux cron (/etc/cron.d/nidp)</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>08:00 IST daily</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Daily</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>0 8 * * *  (IST)</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>Time-based</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>Daily health check that pings every AMC website + AMFI listing candidate URL. Marks JobRun FAILED if any AMC has zero healthy URL candidates — enables early detection of URL rot for mf_disclosure_snapshot and mf_holdings.</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>Health check / URL liveness. No data ingested.</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>Internal operational</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>HTTP pings to ~10 AMC websites (HDFC, ICICI, SBI, Axis, Kotak, Nippon, etc.)</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>nidp.job_log (status only)</t>
+        </is>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>Postgres 16 + TimescaleDB (nidp-postgres, db: nidp)</t>
+        </is>
+      </c>
+      <c r="R45" t="inlineStr">
+        <is>
+          <t>Status write only (no data rows)</t>
+        </is>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>backend/nidp/services/amc_urls_drift_check/</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>None (independent sentinel)</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Alerting / Grafana  •  Indirectly: mf_disclosure_snapshot + mf_holdings depend on healthy URLs</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>~30-60 sec</t>
+        </is>
+      </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>Grafana NIDP Feed Schedule and Status. FAILED = at least one AMC URL is broken.</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>Fix AMC URL in config/seed data. Manual: sudo -u nidp run_service.sh amc_urls_drift_check</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>Currently all 10 AMC scraper URLs are 404 or changed. This check should be alerting daily. See open_bugs.md: AMC scrapers all broken.</t>
         </is>
       </c>
     </row>

--- a/docs/NIDP_FEEDS/Master_Data_Feed_Template.xlsx
+++ b/docs/NIDP_FEEDS/Master_Data_Feed_Template.xlsx
@@ -854,7 +854,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:AB45"/>
+  <dimension ref="A1:AB51"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="18" customWidth="1" style="9" min="1" max="2"/>
@@ -6442,562 +6442,1414 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" t="inlineStr">
+      <c r="A41" s="9" t="inlineStr">
         <is>
           <t>Feed 38</t>
         </is>
       </c>
-      <c r="B41" t="inlineStr">
+      <c r="B41" s="9" t="inlineStr">
         <is>
           <t>V3_SCORES_ENGINE</t>
         </is>
       </c>
-      <c r="C41" t="inlineStr">
+      <c r="C41" s="9" t="inlineStr">
         <is>
           <t>v3_scores_engine</t>
         </is>
       </c>
-      <c r="D41" t="inlineStr">
+      <c r="D41" s="9" t="inlineStr">
         <is>
           <t>PROD</t>
         </is>
       </c>
-      <c r="E41" t="inlineStr">
+      <c r="E41" s="9" t="inlineStr">
         <is>
           <t>Linux cron (/etc/cron.d/nidp)</t>
         </is>
       </c>
-      <c r="F41" t="inlineStr">
+      <c r="F41" s="9" t="inlineStr">
         <is>
           <t>23:55 IST (Mon-Fri)</t>
         </is>
       </c>
-      <c r="G41" t="inlineStr">
+      <c r="G41" s="9" t="inlineStr">
         <is>
           <t>Daily (trading days)</t>
         </is>
       </c>
-      <c r="H41" t="inlineStr">
+      <c r="H41" s="9" t="inlineStr">
         <is>
           <t>55 23 * * 1-5  (IST)</t>
         </is>
       </c>
-      <c r="I41" t="inlineStr">
+      <c r="I41" s="9" t="inlineStr">
         <is>
           <t>Time-based</t>
         </is>
       </c>
-      <c r="J41" t="inlineStr">
+      <c r="J41" s="9" t="inlineStr">
         <is>
           <t>Computes and persists V3 composite Quality + Health scores for every MF scheme and NSE stock. Writes nightly snapshot rows to nidp.v3_mf_scores_daily and nidp.v3_stock_scores_daily.</t>
         </is>
       </c>
-      <c r="K41" t="inlineStr">
+      <c r="K41" s="9" t="inlineStr">
         <is>
           <t>Derived scoring: Quality score (0-100), Health score (0-100) per MF/stock. Served by /v1/{mf,stocks}/scores/*.</t>
         </is>
       </c>
-      <c r="L41" t="inlineStr">
+      <c r="L41" s="9" t="inlineStr">
         <is>
           <t>Internal derived</t>
         </is>
       </c>
-      <c r="N41" t="inlineStr">
+      <c r="N41" s="9" t="inlineStr">
         <is>
           <t>TimescaleDB: nidp.mf_derived_analytics, nidp.stock_features_daily, nidp.technical_indicators</t>
         </is>
       </c>
-      <c r="P41" t="inlineStr">
+      <c r="P41" s="9" t="inlineStr">
         <is>
           <t>nidp.v3_mf_scores_daily  •  nidp.v3_stock_scores_daily</t>
         </is>
       </c>
-      <c r="Q41" t="inlineStr">
+      <c r="Q41" s="9" t="inlineStr">
         <is>
           <t>Postgres 16 + TimescaleDB (nidp-postgres, db: nidp)</t>
         </is>
       </c>
-      <c r="R41" t="inlineStr">
+      <c r="R41" s="9" t="inlineStr">
         <is>
           <t>Insert with date partition; idempotent via ON CONFLICT (date, isin/symbol)</t>
         </is>
       </c>
-      <c r="T41" t="inlineStr">
+      <c r="T41" s="9" t="inlineStr">
         <is>
           <t>backend/nidp/services/v3_scores_engine/</t>
         </is>
       </c>
-      <c r="V41" t="inlineStr">
+      <c r="V41" s="9" t="inlineStr">
         <is>
           <t>mf_derived_refresh (23:50)  •  fundamental_engine (23:05)  •  technical_indicator_engine (22:35)</t>
         </is>
       </c>
-      <c r="W41" t="inlineStr">
+      <c r="W41" s="9" t="inlineStr">
         <is>
           <t>Nivesh portfolio health scoring  •  /api/insights/v3-portfolio  •  intelligence_layer</t>
         </is>
       </c>
-      <c r="Y41" t="inlineStr">
+      <c r="Y41" s="9" t="inlineStr">
         <is>
           <t>~2-5 min</t>
         </is>
       </c>
-      <c r="Z41" t="inlineStr">
+      <c r="Z41" s="9" t="inlineStr">
         <is>
           <t>Grafana NIDP Feed Schedule and Status</t>
         </is>
       </c>
-      <c r="AA41" t="inlineStr">
+      <c r="AA41" s="9" t="inlineStr">
         <is>
           <t>Idempotent. Manual: sudo -u nidp run_service.sh v3_scores_engine</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" t="inlineStr">
+      <c r="A42" s="9" t="inlineStr">
         <is>
           <t>Feed 39</t>
         </is>
       </c>
-      <c r="B42" t="inlineStr">
+      <c r="B42" s="9" t="inlineStr">
         <is>
           <t>ANALYTICS_REFRESH</t>
         </is>
       </c>
-      <c r="C42" t="inlineStr">
+      <c r="C42" s="9" t="inlineStr">
         <is>
           <t>analytics_refresh</t>
         </is>
       </c>
-      <c r="D42" t="inlineStr">
+      <c r="D42" s="9" t="inlineStr">
         <is>
           <t>PROD</t>
         </is>
       </c>
-      <c r="E42" t="inlineStr">
+      <c r="E42" s="9" t="inlineStr">
         <is>
           <t>Linux cron (/etc/cron.d/nidp)</t>
         </is>
       </c>
-      <c r="F42" t="inlineStr">
+      <c r="F42" s="9" t="inlineStr">
         <is>
           <t>00:10 IST (Tue-Sat, i.e. after Mon-Fri trading sessions)</t>
         </is>
       </c>
-      <c r="G42" t="inlineStr">
+      <c r="G42" s="9" t="inlineStr">
         <is>
           <t>Daily (trading days + 1)</t>
         </is>
       </c>
-      <c r="H42" t="inlineStr">
+      <c r="H42" s="9" t="inlineStr">
         <is>
           <t>10 0 * * 2-6  (IST)</t>
         </is>
       </c>
-      <c r="I42" t="inlineStr">
+      <c r="I42" s="9" t="inlineStr">
         <is>
           <t>Time-based</t>
         </is>
       </c>
-      <c r="J42" t="inlineStr">
+      <c r="J42" s="9" t="inlineStr">
         <is>
           <t>Populates analytics.stock_card + analytics.sector_snapshot and refreshes 4 materialized views: mv_top_momentum, mv_delivery_surge, mv_sector_heatmap, mv_fund_category_top10.</t>
         </is>
       </c>
-      <c r="K42" t="inlineStr">
+      <c r="K42" s="9" t="inlineStr">
         <is>
           <t>Derived analytics: momentum, delivery surge, sector heatmap, fund category rankings</t>
         </is>
       </c>
-      <c r="L42" t="inlineStr">
+      <c r="L42" s="9" t="inlineStr">
         <is>
           <t>Internal derived</t>
         </is>
       </c>
-      <c r="N42" t="inlineStr">
+      <c r="N42" s="9" t="inlineStr">
         <is>
           <t>TimescaleDB: nidp.bhavcopy, nidp.delivery, nidp.stock_features_daily, nidp.v3_stock_scores_daily</t>
         </is>
       </c>
-      <c r="P42" t="inlineStr">
+      <c r="P42" s="9" t="inlineStr">
         <is>
           <t>analytics.stock_card  •  analytics.sector_snapshot  •  analytics.mv_top_momentum  •  analytics.mv_delivery_surge  •  analytics.mv_sector_heatmap  •  analytics.mv_fund_category_top10</t>
         </is>
       </c>
-      <c r="Q42" t="inlineStr">
+      <c r="Q42" s="9" t="inlineStr">
         <is>
           <t>Postgres 16 + TimescaleDB (nidp-postgres, db: nidp)</t>
         </is>
       </c>
-      <c r="R42" t="inlineStr">
+      <c r="R42" s="9" t="inlineStr">
         <is>
           <t>Upsert + REFRESH MATERIALIZED VIEW CONCURRENTLY</t>
         </is>
       </c>
-      <c r="T42" t="inlineStr">
+      <c r="T42" s="9" t="inlineStr">
         <is>
           <t>backend/nidp/services/analytics_refresh/</t>
         </is>
       </c>
-      <c r="V42" t="inlineStr">
+      <c r="V42" s="9" t="inlineStr">
         <is>
           <t>v3_scores_engine (23:55)  •  snapshot_builder (22:00)  •  technical_indicator_engine (22:35)</t>
         </is>
       </c>
-      <c r="W42" t="inlineStr">
+      <c r="W42" s="9" t="inlineStr">
         <is>
           <t>DaaS API analytics endpoints  •  market intelligence feeds</t>
         </is>
       </c>
-      <c r="Y42" t="inlineStr">
+      <c r="Y42" s="9" t="inlineStr">
         <is>
           <t>~3-8 min</t>
         </is>
       </c>
-      <c r="Z42" t="inlineStr">
+      <c r="Z42" s="9" t="inlineStr">
         <is>
           <t>Grafana NIDP Feed Schedule and Status</t>
         </is>
       </c>
-      <c r="AA42" t="inlineStr">
+      <c r="AA42" s="9" t="inlineStr">
         <is>
           <t>Idempotent REFRESH + upsert. Manual: sudo -u nidp run_service.sh analytics_refresh</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="A43" t="inlineStr">
+      <c r="A43" s="9" t="inlineStr">
         <is>
           <t>Feed 40</t>
         </is>
       </c>
-      <c r="B43" t="inlineStr">
+      <c r="B43" s="9" t="inlineStr">
         <is>
           <t>PORTFOLIO_TRANSACTIONS_SYNC</t>
         </is>
       </c>
-      <c r="C43" t="inlineStr">
+      <c r="C43" s="9" t="inlineStr">
         <is>
           <t>portfolio_transactions_sync</t>
         </is>
       </c>
-      <c r="D43" t="inlineStr">
+      <c r="D43" s="9" t="inlineStr">
         <is>
           <t>PROD</t>
         </is>
       </c>
-      <c r="E43" t="inlineStr">
+      <c r="E43" s="9" t="inlineStr">
         <is>
           <t>Linux cron (/etc/cron.d/nidp)</t>
         </is>
       </c>
-      <c r="F43" t="inlineStr">
+      <c r="F43" s="9" t="inlineStr">
         <is>
           <t>23:10 IST (Mon-Fri)</t>
         </is>
       </c>
-      <c r="G43" t="inlineStr">
+      <c r="G43" s="9" t="inlineStr">
         <is>
           <t>Daily (trading days)</t>
         </is>
       </c>
-      <c r="H43" t="inlineStr">
+      <c r="H43" s="9" t="inlineStr">
         <is>
           <t>10 23 * * 1-5  (IST)</t>
         </is>
       </c>
-      <c r="I43" t="inlineStr">
+      <c r="I43" s="9" t="inlineStr">
         <is>
           <t>Time-based</t>
         </is>
       </c>
-      <c r="J43" t="inlineStr">
+      <c r="J43" s="9" t="inlineStr">
         <is>
           <t>Reads per-user transaction JSONL exports from GCS and upserts into portfolio.user_transactions_snapshot. Runs after portfolio_holdings_sync to ensure client_master rows exist.</t>
         </is>
       </c>
-      <c r="K43" t="inlineStr">
+      <c r="K43" s="9" t="inlineStr">
         <is>
           <t>Per-user transactions: buy/sell/switch/dividend history. PII.</t>
         </is>
       </c>
-      <c r="L43" t="inlineStr">
+      <c r="L43" s="9" t="inlineStr">
         <is>
           <t>Internal (per-user PII)</t>
         </is>
       </c>
-      <c r="N43" t="inlineStr">
+      <c r="N43" s="9" t="inlineStr">
         <is>
           <t>GCS landing zone: gs://{NIDP_GCS_BUCKET}/portfolio/transactions/{date}/transactions.jsonl</t>
         </is>
       </c>
-      <c r="P43" t="inlineStr">
+      <c r="P43" s="9" t="inlineStr">
         <is>
           <t>portfolio.user_transactions_snapshot</t>
         </is>
       </c>
-      <c r="Q43" t="inlineStr">
+      <c r="Q43" s="9" t="inlineStr">
         <is>
           <t>Postgres 16 + TimescaleDB (nidp-postgres, db: nidp)</t>
         </is>
       </c>
-      <c r="R43" t="inlineStr">
+      <c r="R43" s="9" t="inlineStr">
         <is>
           <t>Upsert with dedup hash</t>
         </is>
       </c>
-      <c r="T43" t="inlineStr">
+      <c r="T43" s="9" t="inlineStr">
         <is>
           <t>backend/nidp/services/portfolio_transactions_sync/</t>
         </is>
       </c>
-      <c r="V43" t="inlineStr">
+      <c r="V43" s="9" t="inlineStr">
         <is>
           <t>portfolio_holdings_sync (23:00) — must succeed first</t>
         </is>
       </c>
-      <c r="W43" t="inlineStr">
+      <c r="W43" s="9" t="inlineStr">
         <is>
           <t>portfolio_intelligence_sync  •  tax engine  •  performance analytics</t>
         </is>
       </c>
-      <c r="Z43" t="inlineStr">
+      <c r="Z43" s="9" t="inlineStr">
         <is>
           <t>Grafana NIDP Feed Schedule and Status</t>
         </is>
       </c>
-      <c r="AA43" t="inlineStr">
+      <c r="AA43" s="9" t="inlineStr">
         <is>
           <t>Idempotent. Manual: sudo -u nidp run_service.sh portfolio_transactions_sync</t>
         </is>
       </c>
-      <c r="AB43" t="inlineStr">
+      <c r="AB43" s="9" t="inlineStr">
         <is>
           <t>BLOCKED by portfolio_holdings_sync GCS 404 failure. Fix GCS export in Nivesh app first.</t>
         </is>
       </c>
     </row>
     <row r="44">
-      <c r="A44" t="inlineStr">
+      <c r="A44" s="9" t="inlineStr">
         <is>
           <t>Feed 41</t>
         </is>
       </c>
-      <c r="B44" t="inlineStr">
+      <c r="B44" s="9" t="inlineStr">
         <is>
           <t>PORTFOLIO_GOALS_SYNC</t>
         </is>
       </c>
-      <c r="C44" t="inlineStr">
+      <c r="C44" s="9" t="inlineStr">
         <is>
           <t>portfolio_goals_sync</t>
         </is>
       </c>
-      <c r="D44" t="inlineStr">
+      <c r="D44" s="9" t="inlineStr">
         <is>
           <t>PROD</t>
         </is>
       </c>
-      <c r="E44" t="inlineStr">
+      <c r="E44" s="9" t="inlineStr">
         <is>
           <t>Linux cron (/etc/cron.d/nidp)</t>
         </is>
       </c>
-      <c r="F44" t="inlineStr">
+      <c r="F44" s="9" t="inlineStr">
         <is>
           <t>23:15 IST (Mon-Fri)</t>
         </is>
       </c>
-      <c r="G44" t="inlineStr">
+      <c r="G44" s="9" t="inlineStr">
         <is>
           <t>Daily (trading days)</t>
         </is>
       </c>
-      <c r="H44" t="inlineStr">
+      <c r="H44" s="9" t="inlineStr">
         <is>
           <t>15 23 * * 1-5  (IST)</t>
         </is>
       </c>
-      <c r="I44" t="inlineStr">
+      <c r="I44" s="9" t="inlineStr">
         <is>
           <t>Time-based</t>
         </is>
       </c>
-      <c r="J44" t="inlineStr">
+      <c r="J44" s="9" t="inlineStr">
         <is>
           <t>Syncs per-user goal definitions from Nivesh PG (user_goals) to NIDP so the intelligence_layer can evaluate goal alignment and compute on_track_pct.</t>
         </is>
       </c>
-      <c r="K44" t="inlineStr">
+      <c r="K44" s="9" t="inlineStr">
         <is>
           <t>Per-user goals: target amount, horizon, current corpus, SIP, on-track %. PII.</t>
         </is>
       </c>
-      <c r="L44" t="inlineStr">
+      <c r="L44" s="9" t="inlineStr">
         <is>
           <t>Internal (per-user PII)</t>
         </is>
       </c>
-      <c r="N44" t="inlineStr">
+      <c r="N44" s="9" t="inlineStr">
         <is>
           <t>Nivesh Postgres: user_goals table (GCS or direct PG bridge)</t>
         </is>
       </c>
-      <c r="P44" t="inlineStr">
+      <c r="P44" s="9" t="inlineStr">
         <is>
           <t>portfolio.user_goals_snapshot</t>
         </is>
       </c>
-      <c r="Q44" t="inlineStr">
+      <c r="Q44" s="9" t="inlineStr">
         <is>
           <t>Postgres 16 + TimescaleDB (nidp-postgres, db: nidp)</t>
         </is>
       </c>
-      <c r="R44" t="inlineStr">
+      <c r="R44" s="9" t="inlineStr">
         <is>
           <t>Upsert</t>
         </is>
       </c>
-      <c r="T44" t="inlineStr">
+      <c r="T44" s="9" t="inlineStr">
         <is>
           <t>backend/nidp/services/portfolio_goals_sync/</t>
         </is>
       </c>
-      <c r="V44" t="inlineStr">
+      <c r="V44" s="9" t="inlineStr">
         <is>
           <t>portfolio_holdings_sync (23:00)  •  portfolio_transactions_sync (23:10)</t>
         </is>
       </c>
-      <c r="W44" t="inlineStr">
+      <c r="W44" s="9" t="inlineStr">
         <is>
           <t>intelligence_layer (23:20)  •  portfolio_intelligence_sync (23:30)  •  Goal Alignment Engine</t>
         </is>
       </c>
-      <c r="Z44" t="inlineStr">
+      <c r="Z44" s="9" t="inlineStr">
         <is>
           <t>Grafana NIDP Feed Schedule and Status</t>
         </is>
       </c>
-      <c r="AA44" t="inlineStr">
+      <c r="AA44" s="9" t="inlineStr">
         <is>
           <t>Idempotent. Manual: sudo -u nidp run_service.sh portfolio_goals_sync</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="A45" t="inlineStr">
+      <c r="A45" s="9" t="inlineStr">
         <is>
           <t>Feed 42</t>
         </is>
       </c>
-      <c r="B45" t="inlineStr">
+      <c r="B45" s="9" t="inlineStr">
         <is>
           <t>AMC_URLS_DRIFT_CHECK</t>
         </is>
       </c>
-      <c r="C45" t="inlineStr">
+      <c r="C45" s="9" t="inlineStr">
         <is>
           <t>amc_urls_drift_check</t>
         </is>
       </c>
-      <c r="D45" t="inlineStr">
+      <c r="D45" s="9" t="inlineStr">
         <is>
           <t>PROD</t>
         </is>
       </c>
-      <c r="E45" t="inlineStr">
+      <c r="E45" s="9" t="inlineStr">
         <is>
           <t>Linux cron (/etc/cron.d/nidp)</t>
         </is>
       </c>
-      <c r="F45" t="inlineStr">
+      <c r="F45" s="9" t="inlineStr">
         <is>
           <t>08:00 IST daily</t>
         </is>
       </c>
-      <c r="G45" t="inlineStr">
+      <c r="G45" s="9" t="inlineStr">
         <is>
           <t>Daily</t>
         </is>
       </c>
-      <c r="H45" t="inlineStr">
+      <c r="H45" s="9" t="inlineStr">
         <is>
           <t>0 8 * * *  (IST)</t>
         </is>
       </c>
-      <c r="I45" t="inlineStr">
+      <c r="I45" s="9" t="inlineStr">
         <is>
           <t>Time-based</t>
         </is>
       </c>
-      <c r="J45" t="inlineStr">
+      <c r="J45" s="9" t="inlineStr">
         <is>
           <t>Daily health check that pings every AMC website + AMFI listing candidate URL. Marks JobRun FAILED if any AMC has zero healthy URL candidates — enables early detection of URL rot for mf_disclosure_snapshot and mf_holdings.</t>
         </is>
       </c>
-      <c r="K45" t="inlineStr">
+      <c r="K45" s="9" t="inlineStr">
         <is>
           <t>Health check / URL liveness. No data ingested.</t>
         </is>
       </c>
-      <c r="L45" t="inlineStr">
+      <c r="L45" s="9" t="inlineStr">
         <is>
           <t>Internal operational</t>
         </is>
       </c>
-      <c r="N45" t="inlineStr">
+      <c r="N45" s="9" t="inlineStr">
         <is>
           <t>HTTP pings to ~10 AMC websites (HDFC, ICICI, SBI, Axis, Kotak, Nippon, etc.)</t>
         </is>
       </c>
-      <c r="P45" t="inlineStr">
+      <c r="P45" s="9" t="inlineStr">
         <is>
           <t>nidp.job_log (status only)</t>
         </is>
       </c>
-      <c r="Q45" t="inlineStr">
+      <c r="Q45" s="9" t="inlineStr">
         <is>
           <t>Postgres 16 + TimescaleDB (nidp-postgres, db: nidp)</t>
         </is>
       </c>
-      <c r="R45" t="inlineStr">
+      <c r="R45" s="9" t="inlineStr">
         <is>
           <t>Status write only (no data rows)</t>
         </is>
       </c>
-      <c r="T45" t="inlineStr">
+      <c r="T45" s="9" t="inlineStr">
         <is>
           <t>backend/nidp/services/amc_urls_drift_check/</t>
         </is>
       </c>
-      <c r="V45" t="inlineStr">
+      <c r="V45" s="9" t="inlineStr">
         <is>
           <t>None (independent sentinel)</t>
         </is>
       </c>
-      <c r="W45" t="inlineStr">
+      <c r="W45" s="9" t="inlineStr">
         <is>
           <t>Alerting / Grafana  •  Indirectly: mf_disclosure_snapshot + mf_holdings depend on healthy URLs</t>
         </is>
       </c>
-      <c r="Y45" t="inlineStr">
+      <c r="Y45" s="9" t="inlineStr">
         <is>
           <t>~30-60 sec</t>
         </is>
       </c>
-      <c r="Z45" t="inlineStr">
+      <c r="Z45" s="9" t="inlineStr">
         <is>
           <t>Grafana NIDP Feed Schedule and Status. FAILED = at least one AMC URL is broken.</t>
         </is>
       </c>
-      <c r="AA45" t="inlineStr">
+      <c r="AA45" s="9" t="inlineStr">
         <is>
           <t>Fix AMC URL in config/seed data. Manual: sudo -u nidp run_service.sh amc_urls_drift_check</t>
         </is>
       </c>
-      <c r="AB45" t="inlineStr">
+      <c r="AB45" s="9" t="inlineStr">
         <is>
           <t>Currently all 10 AMC scraper URLs are 404 or changed. This check should be alerting daily. See open_bugs.md: AMC scrapers all broken.</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Feed 43</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>SCREENER_QUARTERLY_BALANCE_SHEET</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>screener_in_bs</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>PROD</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>Embedded in NSE_FINANCIALS service (service.py strategy 2)</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>On NSE quarterly earnings announcement</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Event-driven (announcement classifier trigger)</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>N/A — event-driven</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>Event-driven</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>Parses the #balance-sheet section of screener.in company page and writes annual balance sheet entries per symbol. Called as a supplemental step alongside quarterly P&amp;L parsing in service.py strategy 2 (screener path). Uses source tag "screener_in_bs". Wired 2026-05-27.</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>Annual balance sheet data: total_assets_cr, total_equity_cr, long_term_debt_cr, short_term_debt_cr, total_liabilities_cr, cash_and_equivalents_cr, net_worth_cr.</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>Public financial data</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>Nivesh NIDP Platform</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>screener.in (authenticated session — session cookie required)</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>screener.in #balance-sheet HTML section</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>nidp.nse_financials_quarterly (source="screener_in_bs", period_type="annual")</t>
+        </is>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>Postgres 16 + TimescaleDB on nidp-stack-vm</t>
+        </is>
+      </c>
+      <c r="R46" t="inlineStr">
+        <is>
+          <t>UPSERT — ON CONFLICT (symbol, period_end, consolidated) DO UPDATE with COALESCE</t>
+        </is>
+      </c>
+      <c r="S46" t="inlineStr">
+        <is>
+          <t>Varies — depends on announcement frequency</t>
+        </is>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>backend/nidp/services/nse_financials/llm_extractor.py (parse_screener_balance_sheet) • backend/nidp/services/nse_financials/service.py (strategy 2 caller)</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>_parse_screener_section(html, "balance-sheet") → extract total_assets, equity, LT/ST debt, cash, net_worth → write annual records with upsert_financials(source="screener_in_bs")</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>NSE_FINANCIALS (primary P&amp;L quarterly parser)</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>populate_stock_features_extended (reads balance sheet cols for D/E) • fundamental_engine (Altman Z uses balance sheet)</t>
+        </is>
+      </c>
+      <c r="X46" t="inlineStr">
+        <is>
+          <t>NIDP Backend</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>~0.5 sec per symbol (incremental)</t>
+        </is>
+      </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>nidp.job_log per NSE_FINANCIALS run</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>Re-run NSE_FINANCIALS for the date. Idempotent UPSERT with COALESCE (null-safe).</t>
+        </is>
+      </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>⚠️ DEPENDS ON: screener.in session cookie in NIDP_SCREENER_SESSION_ID env var. Cookie expires ~2026-06. Wired 2026-05-27. Historical backfill separately tracked (screener_backfill_historical job).</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Feed 44</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>SCREENER_ANNUAL_PROFIT_LOSS</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>screener_in_annual</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>PROD</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>Embedded in NSE_FINANCIALS service (service.py strategy 2)</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>On NSE quarterly earnings announcement</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Event-driven (announcement classifier trigger)</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>N/A — event-driven</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>Event-driven</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>Parses the #profit-loss section of screener.in company page for annual (FY) P&amp;L data. Writes annual revenue, EBITDA, PAT, EPS per symbol. Source tag "screener_in_annual". Wired 2026-05-27.</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>Annual P&amp;L: revenue_from_ops_cr, total_expenses_cr, ebitda_cr, other_income_cr, finance_costs_cr, depreciation_cr, pbt_cr, pat_cr, eps_basic.</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>Public financial data</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>Nivesh NIDP Platform</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>screener.in (authenticated session)</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>screener.in #profit-loss HTML section (annual tab)</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>nidp.nse_financials_quarterly (source="screener_in_annual", period_type="annual")</t>
+        </is>
+      </c>
+      <c r="Q47" t="inlineStr">
+        <is>
+          <t>Postgres 16 + TimescaleDB on nidp-stack-vm</t>
+        </is>
+      </c>
+      <c r="R47" t="inlineStr">
+        <is>
+          <t>UPSERT — COALESCE on conflict</t>
+        </is>
+      </c>
+      <c r="S47" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>backend/nidp/services/nse_financials/llm_extractor.py (parse_screener_profit_loss — NEW 2026-05-27) • backend/nidp/services/nse_financials/backfill_screener_historical.py</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>_parse_screener_section(html, "profit-loss") → map column labels to FY dates → extract revenue/EBITDA/PAT/EPS → filter since_year → upsert with source="screener_in_annual"</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>NSE_FINANCIALS</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>populate_stock_features_v3 (revenue_growth_3y_cagr, profit_margin_trend, debt_trend) • v3_scores_engine (Health score primitives)</t>
+        </is>
+      </c>
+      <c r="X47" t="inlineStr">
+        <is>
+          <t>NIDP Backend</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>~0.5 sec per symbol</t>
+        </is>
+      </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>nidp.job_log per NSE_FINANCIALS run</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>Re-run NSE_FINANCIALS. Idempotent UPSERT.</t>
+        </is>
+      </c>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>⚠️ NEW 2026-05-27: parse_screener_profit_loss() function added to llm_extractor.py. Unlocks revenue_growth_3y_cagr, profit_margin_trend_pct, debt_trend_pct primitives. 44-test suite in tests/test_nidp_screener_parsers.py (all passing).</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Feed 45</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>SCREENER_SHAREHOLDING</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>screener_in</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>PROD</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>Embedded in NSE_FINANCIALS service (service.py strategy 2)</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>On NSE quarterly earnings announcement</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Event-driven</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>N/A — event-driven</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>Event-driven</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>Parses the #shareholding section of screener.in for promoter %, FII %, DII %, public % per quarter. Wired 2026-05-27 — previously existed in llm_extractor.py but was never called in service.py.</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>Quarterly shareholding pattern: promoter_pct, fii_pct, dii_pct, public_pct per (symbol, quarter).</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>Public data</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>Nivesh NIDP Platform</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>screener.in (authenticated session)</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>screener.in #shareholding HTML section</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>nidp.nse_shareholding</t>
+        </is>
+      </c>
+      <c r="Q48" t="inlineStr">
+        <is>
+          <t>Postgres 16 + TimescaleDB on nidp-stack-vm</t>
+        </is>
+      </c>
+      <c r="R48" t="inlineStr">
+        <is>
+          <t>UPSERT</t>
+        </is>
+      </c>
+      <c r="S48" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>backend/nidp/services/nse_financials/llm_extractor.py (parse_screener_shareholding) • backend/nidp/services/nse_financials/service.py (strategy 2 caller — wired 2026-05-27)</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>_parse_screener_section(html, "shareholding") → map quarters → extract promoter/FII/DII/public → upsert_shareholding()</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>NSE_FINANCIALS</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>populate_stock_features_extended (reads promoter_pct for quality score) • v3_scores_engine (promoter_pct primitive)</t>
+        </is>
+      </c>
+      <c r="X48" t="inlineStr">
+        <is>
+          <t>NIDP Backend</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>~0.3 sec per symbol</t>
+        </is>
+      </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>nidp.job_log per NSE_FINANCIALS run</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>Re-run NSE_FINANCIALS. Idempotent.</t>
+        </is>
+      </c>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>⚠️ parse_screener_shareholding() already existed but was never wired into service.py. Fixed 2026-05-27. promoter_pct was 9% coverage before this fix; expected 85%+ after full backfill.</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Feed 46 (BACKFILL — one-time)</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>SCREENER_HISTORICAL_BACKFILL</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>screener_backfill_historical</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>PROD / MANUAL</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>Manual invocation from nidp-stack-vm (Docker container)</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>One-time + periodic re-run</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Manual</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>Manual trigger</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>Bulk historical backfill of Screener.in quarterly P&amp;L + balance sheet + annual P&amp;L + shareholding for all 504 Nifty 500 symbols. Tier-ordered (T0=Nifty50 first). Rate-limit aware — halts on detection, resumes without --force on re-run.</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>12 quarters per symbol of quarterly financials; ~9 annual balance sheet entries; ~7 annual P&amp;L entries; ~12 shareholding quarters. Source tags: screener_in / screener_in_bs / screener_in_annual.</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>Public financial data</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>Nivesh NIDP Platform</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>screener.in (authenticated session — cookie in NIDP_SCREENER_SESSION_ID)</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>screener.in company pages (#quarters, #balance-sheet, #profit-loss, #shareholding sections)</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>nidp.nse_financials_quarterly  •  nidp.nse_shareholding</t>
+        </is>
+      </c>
+      <c r="Q49" t="inlineStr">
+        <is>
+          <t>Postgres 16 + TimescaleDB on nidp-stack-vm</t>
+        </is>
+      </c>
+      <c r="R49" t="inlineStr">
+        <is>
+          <t>UPSERT — idempotent COALESCE-based merge</t>
+        </is>
+      </c>
+      <c r="S49" t="inlineStr">
+        <is>
+          <t>504 symbols × (12 Q + 9 BS + 7 PL + 12 SHP) ≈ 20,160 total records</t>
+        </is>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>backend/nidp/services/nse_financials/backfill_screener_historical.py</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>For each symbol in tier order: fetch screener.in HTML → parse_all_screener_quarters + parse_screener_balance_sheet + parse_screener_profit_loss + parse_screener_shareholding → upsert all four → 4s delay → rate-limit check → halt on trigger.</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>None — primary external source. Requires screener.in session cookie.</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>populate_stock_features_extended + populate_stock_features_v3 + v3_scores_engine (must run after backfill to recompute primitives and scores)</t>
+        </is>
+      </c>
+      <c r="X49" t="inlineStr">
+        <is>
+          <t>NIDP Backend</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>~4 sec/symbol × 504 ≈ ~34 min total (incl. rate-limit pauses)</t>
+        </is>
+      </c>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t>Console logs via nidp.job_log; exception_queue on failures</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>Re-run with: docker exec nidp-console python3 -m nidp.services.nse_financials.backfill_screener_historical --nifty500 --since 2023-05-28 --delay-ms 4000 (without --force to skip already-backfilled).</t>
+        </is>
+      </c>
+      <c r="AB49" t="inlineStr">
+        <is>
+          <t>🔄 RUNNING 2026-05-27. 213/504 symbols processed in first run; rate-limited on APTUS in T3. Resume run in progress with --delay-ms 4000. KNOWN ISSUES: BAJAJFINSV slug wrong (not_found); M&amp;M not found (&amp; in URL); several NBFC/insurance symbols return 0 quarters (date window issue). After completion, must run: populate_stock_features_extended → populate_stock_features_v3 → v3_scores_engine.</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Feed 47 (NOT IN cron — MISSING)</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>POPULATE_STOCK_FEATURES_EXTENDED</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>populate_stock_features_extended</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>PROD</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>Linux cron (/etc/cron.d/nidp) — CURRENTLY MISSING</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>23:10 IST (Mon-Fri) RECOMMENDED</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Daily (trading days)</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>NOT SCHEDULED</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>Time-based (required)</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>SQL function nidp.populate_stock_features_extended(date) that joins fundamentals + shareholding + market cap into stock_features_daily rows. Computes ROE, D/E, market_cap_bucket, promoter_pct. Must run after fundamental_engine and before populate_stock_features_v3.</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>Updates stock_features_daily: roe_pct, debt_to_equity, market_cap_bucket, promoter_pct, short_term_debt_cr, long_term_debt_cr columns.</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>Internal derived</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>Nivesh NIDP Platform</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>nidp.v_stock_fundamentals_latest (quarterly-filtered fundamental view) + nse_shareholding + prices_eod</t>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>nidp.v_stock_fundamentals_latest  •  nidp.nse_shareholding  •  nidp.prices_eod</t>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>nidp.stock_features_daily (UPDATE — fundamental + shareholding columns)</t>
+        </is>
+      </c>
+      <c r="Q50" t="inlineStr">
+        <is>
+          <t>Postgres 16 + TimescaleDB on nidp-stack-vm</t>
+        </is>
+      </c>
+      <c r="R50" t="inlineStr">
+        <is>
+          <t>SQL UPDATE (in-place on existing rows)</t>
+        </is>
+      </c>
+      <c r="S50" t="inlineStr">
+        <is>
+          <t>~504 symbols/day</t>
+        </is>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>backend/nidp/migrations/*.sql (function definition)  •  called via conn.execute()</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>SELECT nidp.populate_stock_features_extended(date) — joins fundamentals view → updates D/E, ROE, market cap bucket, promoter in stock_features_daily.</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>fundamental_engine (must have run first)</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>populate_stock_features_v3 (reads updated columns)  •  v3_scores_engine (Quality score primitives)</t>
+        </is>
+      </c>
+      <c r="X50" t="inlineStr">
+        <is>
+          <t>NIDP Backend</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>~2-5 sec</t>
+        </is>
+      </c>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>⚠️ NOT MONITORED — not in cron, no job_log entry</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>Manual: SELECT nidp.populate_stock_features_extended('2026-05-25'::date); — run from psql on nidp-postgres.</t>
+        </is>
+      </c>
+      <c r="AB50" t="inlineStr">
+        <is>
+          <t>🚨 MISSING FROM CRON (NIDP-T29). Without this, roe_pct / debt_to_equity / market_cap_bucket / promoter_pct stay 0% covered even though screener backfill has populated nse_financials_quarterly. Add to cron AFTER fundamental_engine (23:05 IST) and BEFORE v3_scores_engine (23:55 IST).</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Feed 48 (NOT IN cron — MISSING)</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>POPULATE_STOCK_FEATURES_V3</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>populate_stock_features_v3</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>PROD</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>Linux cron (/etc/cron.d/nidp) — CURRENTLY MISSING</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>23:20 IST (Mon-Fri) RECOMMENDED</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Daily (trading days)</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>NOT SCHEDULED</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>Time-based (required)</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>SQL function nidp.populate_stock_features_v3(date) that computes 3-year CAGR metrics (revenue_growth, EPS growth), margin trend, and debt trend from annual financial data. Must run after populate_stock_features_extended and before v3_scores_engine.</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>Updates stock_features_daily: revenue_growth_3y_cagr_pct, profit_margin_trend_pct, debt_trend_pct columns (Health score primitives).</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>Internal derived</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>Nivesh NIDP Platform</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>nidp.nse_financials_quarterly (annual P&amp;L records, source=screener_in_annual)</t>
+        </is>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>nidp.nse_financials_quarterly (period_type=annual)</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>nidp.stock_features_daily (UPDATE — V3 Health score primitive columns)</t>
+        </is>
+      </c>
+      <c r="Q51" t="inlineStr">
+        <is>
+          <t>Postgres 16 + TimescaleDB on nidp-stack-vm</t>
+        </is>
+      </c>
+      <c r="R51" t="inlineStr">
+        <is>
+          <t>SQL UPDATE</t>
+        </is>
+      </c>
+      <c r="S51" t="inlineStr">
+        <is>
+          <t>~504 symbols/day</t>
+        </is>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>backend/nidp/migrations/*.sql (function definition)</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>SELECT nidp.populate_stock_features_v3(date) — reads annual P&amp;L rows → computes OLS-based CAGR over 3Y → updates Health score primitive columns.</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>populate_stock_features_extended (must have run first)</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>v3_scores_engine (Health score: revenue_growth, margin_trend, debt_trend)</t>
+        </is>
+      </c>
+      <c r="X51" t="inlineStr">
+        <is>
+          <t>NIDP Backend</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>~2-5 sec</t>
+        </is>
+      </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>⚠️ NOT MONITORED — not in cron</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>Manual: SELECT nidp.populate_stock_features_v3('2026-05-25'::date);</t>
+        </is>
+      </c>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>🚨 MISSING FROM CRON (NIDP-T29). Revenue growth, margin trend, debt trend all 0% coverage without this function running daily. Add after populate_stock_features_extended, before v3_scores_engine.</t>
         </is>
       </c>
     </row>
@@ -7024,7 +7876,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L35"/>
+  <dimension ref="A1:L38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" style="10" min="1" max="1"/>
@@ -9094,6 +9946,192 @@
         </is>
       </c>
     </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Stock scoring</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>v3_stock_scores_daily</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>table</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>nidp</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>~504/day (growing)</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>~1 MB</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>V3 Quality + Health scores per stock per day. Quality score (0-100) from 6 primitives: roe_pct (25%), debt_to_equity (15%), eps_growth_3y_cagr (20%), promoter_pct (10%), market_cap_bucket (10%), earnings_consistency_score (20%). Health score (0-100) from 6 primitives: revenue_growth_3y_cagr (25%), profit_margin_trend (20%), debt_trend (15%), earnings_surprise_pct (15%), volatility_1y (10%), dividend_yield (5%). Also stores coverage_pct per score.</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>v3_scores_engine (23:55 IST Mon-Fri)</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>Copilot stock recommendations  •  Nivesh portfolio health  •  /api/insights/v3-portfolio</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>LIVE as of 2026-05-27. Coverage improving as screener backfill completes. earnings_surprise_pct primitive still 0% (no consensus EPS source — see NIDP-T30). ⚠️ Score band calibration needed once backfill is complete (may cluster near 50 — see NIDP-T32).</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Stock scoring</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>nse_financials_quarterly</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>table</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>nidp</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>~120,000+ (post-backfill)</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>~80 MB</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>Central financial data table. Holds per-symbol quarterly P&amp;L (source=screener_in, period_type=QUARTERLY), annual balance sheet (source=screener_in_bs, period_type=annual), annual P&amp;L (source=screener_in_annual, period_type=annual), and NSE XBRL rows. UPSERT key: (symbol, period_end, consolidated). COALESCE merge — never overwrites existing non-null.</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>NSE_FINANCIALS (quarterly P&amp;L via screener.in, triggered on announcements)  •  SCREENER_QUARTERLY_BALANCE_SHEET (new 2026-05-27)  •  SCREENER_ANNUAL_PROFIT_LOSS (new 2026-05-27)  •  NSE_XBRL_PARSER (integrated XBRL from NSE announcements)</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>fundamental_engine (Piotroski/Altman)  •  populate_stock_features_extended  •  populate_stock_features_v3  •  v3_scores_engine  •  Copilot fundamentals card</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>Data quality improved significantly on 2026-05-27. ⚠️ v_stock_fundamentals_latest view filters period_type ~~* QUARTERLY — annual records are invisible to this view. Annual data merged into quarterly rows via _match_balance_sheet(). ⚠️ BAJAJFINSV slug missing from _SCREENER_SLUG_MAP (see NIDP-T28).</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>V3 primitives — coverage</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>stock primitive coverage (post-backfill)</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>derived metric</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>nidp</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>V3 Quality primitives: roe_pct ~85%+, debt_to_equity ~85%+, eps_growth_3y_cagr 91%, promoter_pct ~85%+, market_cap_bucket ~85%+, earnings_consistency_score 93%. V3 Health primitives: revenue_growth_3y_cagr ~60%+, profit_margin_trend ~70%+, debt_trend ~70%+, earnings_surprise_pct 0% (no source), volatility_1y 100%, dividend_yield 100%. Pre-backfill: roe_pct was 0%, debt_to_equity was 0%, market_cap_bucket was 0%, promoter_pct was 9%.</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>populate_stock_features_extended (roe, D/E, market_cap, promoter)  •  populate_stock_features_v3 (revenue growth, margin trend, debt trend)</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>v3_scores_engine  •  Copilot recommendations quality tier</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>Coverage targets achieved on 2026-05-27 after Screener.in full-parser wire-up. ⚠️ earnings_surprise_pct permanently 0% — needs consensus EPS estimates data source (NIDP-T30). ⚠️ Cron for populate_stock_features_extended and populate_stock_features_v3 not yet added (NIDP-T29). ⚠️ Score band calibration required before surfacing in UI (NIDP-T32).</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:L1"/>
@@ -9108,7 +10146,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M31"/>
+  <dimension ref="A1:M43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" style="10" min="1" max="1"/>
@@ -11021,6 +12059,810 @@
         </is>
       </c>
     </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>NIDP-T28</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Config Bug</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>screener_backfill_historical</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>BAJAJFINSV slug wrong — returns not_found on Screener.in</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>backfill_screener_historical logs: FEED FAILURE [tier=0] BAJAJFINSV: symbol not found on Screener.in. BAJAJFINSV is a Nifty 50 constituent — a P0 gap.</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Screener.in uses the slug BAJAJ-FINSERV for this company. The _SCREENER_SLUG_MAP in ir_scraper.py has no entry for BAJAJFINSV, so it falls through to the default URL template which produces a 404.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>Add 'BAJAJFINSV': 'BAJAJ-FINSERV' to _SCREENER_SLUG_MAP in backend/nidp/services/nse_financials/ir_scraper.py. (~15 min) Then re-run backfill for BAJAJFINSV: --symbols BAJAJFINSV --force</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>Audit _SCREENER_SLUG_MAP systematically: for every not_found in exception_queue where tier=0 or tier=1, verify the Screener.in slug manually and add to the map. Add a CI test that fetches the first result for each mapped slug and confirms 200. (~1 day)</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>backend/nidp/services/nse_financials/ir_scraper.py (_SCREENER_SLUG_MAP dict)</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>NIDP Backend</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>Also likely affects M&amp;M (special char in name). Check exception_queue for all tier=0 not_found outcomes.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>NIDP-T29</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Wiring Missing</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>populate_stock_features_extended + populate_stock_features_v3</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Both SQL functions missing from daily cron — Quality/Health primitives never recomputed</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>roe_pct, debt_to_equity, market_cap_bucket, promoter_pct, revenue_growth_3y_cagr, profit_margin_trend_pct, debt_trend_pct all have 0% coverage on any day the backfill added data, because the SQL functions that compute them are never called by cron.</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>populate_stock_features_extended() and populate_stock_features_v3() are SQL functions that must be explicitly called per date. They exist in the DB but no Python service and no cron entry invokes them daily. v3_scores_engine depends on their output — without them, 7 of 12 primitives are permanently NULL.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>Add two cron entries to /etc/cron.d/nidp and backend/nidp/deploy/vm/nidp.cron: (1) populate_stock_features_extended at 23:10 IST (after fundamental_engine 23:05, before v3_scores 23:55) (2) populate_stock_features_v3 at 23:20 IST. Each entry: run_service.sh populate_features --date $(date +%F) calling the relevant SQL function. (~1 day)</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>Add a dedicated populate_features service that: (a) calls both functions sequentially, (b) logs to job_log, (c) has Grafana monitoring. Long-term: fold into fundamental_engine as a post-compute step. (~2 days)</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>backend/nidp/deploy/vm/nidp.cron  •  /etc/cron.d/nidp on nidp-stack-vm</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>NIDP Backend</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>Discovered 2026-05-27. Without this fix, even a successful screener backfill produces 0% coverage on the V3 quality/health primitives because stock_features_daily rows are never updated with the fundamental data. Highest-leverage 1-day fix for V3 score quality.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>NIDP-T30</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Upstream Data Gap</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>v3_scores_engine (Health score)</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>earnings_surprise_pct primitive permanently 0% — no consensus EPS estimates source</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>earnings_surprise_pct has been 0% coverage since V3 launch. This is 15% of the Health score. Every stock health score is effectively computed on 85% of its weight, and the missing 15% defaults to the null fallback (50), potentially distorting rankings.</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>earnings_surprise_pct requires quarterly consensus EPS estimates (street estimates, not actuals). NSE does not publish consensus data. Screener.in ratios section has TTM EPS but no estimates. No current data source in NIDP provides this.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>Short-term: reduce the weight of earnings_surprise_pct to 0% and redistribute across other primitives, OR set a "data_unavailable" flag so the score is explicitly computed on available primitives only. Document the gap prominently. (~1 day)</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>Long-term: procure quarterly consensus EPS estimates from a data vendor. Options: (a) Bloomberg API (expensive, institutional), (b) Refinitiv/LSEG (enterprise), (c) NSE India API (if available post-XBRL standardization), (d) Use realized EPS surprises from XBRL (compare declared EPS vs prior quarter estimate if ever stored). (2-4 weeks for vendor evaluation)</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>backend/nidp/services/v3_scores_engine/  •  nidp.stock_features_daily (earnings_surprise_pct column)</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>NIDP Platform / Business Decision</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>Blocks Health score being fully representative. Must be disclosed in any V3 scoring documentation exposed to users. Pair with NIDP-T33 (ranking gate) and NIDP-T32 (score calibration).</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>NIDP-T31</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Ops / Security</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>screener_backfill_historical + NSE_FINANCIALS</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Screener.in session cookie expiry — current cookie expires ~2026-06, no rotation automation</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>NIDP_SCREENER_SESSION_ID cookie manually obtained from DevTools. All screener.in parsing (quarterly P&amp;L, balance sheet, shareholding, backfill) silently 401 or return login-page HTML when the cookie expires. Expiry is ~2026-06 (approximately 30 days from 2026-05-27 issue date).</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Screener.in uses session-based auth with a ~30-60 day cookie lifetime. No API key alternative available on free/paid plans. Cookie refresh requires manual browser login.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>Short-term: Set a calendar reminder for 2026-06-10 (10 days before expected expiry). Manually refresh the cookie via DevTools and update NIDP_SCREENER_COOKIE env var on nidp-stack-vm. (~30 min)</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>Long-term: Build a headless-browser based auto-login: (a) Playwright script logs in with stored credentials (separate secret in GCP Secret Manager), (b) extracts session cookie, (c) updates NIDP_SCREENER_SESSION_ID in the running container env, (d) runs as a monthly scheduled Cloud Run job. Add alerting: if screener.in fetch returns login-page HTML, emit CRITICAL alert. (~3 days)</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>backend/nidp/services/nse_financials/ir_scraper.py (cookie loading)  •  nidp.env  •  New: backend/nidp/services/screener_cookie_refresh/ (Playwright automation)</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>NIDP Backend</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>⚠️ TIME-SENSITIVE: Cookie expires approximately 2026-06. Schedule rotation before then. Credentials are stored in nidp.env on nidp-stack-vm (not committed to git).</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>NIDP-T32</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Data Quality</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>v3_scores_engine</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Score band calibration needed — distribution may cluster near 50 (null-fallback value)</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>V3 scores historically defaulted null primitives to 50 (the midpoint). As real data backfills in, score distributions may not cluster correctly around expected percentile bands. Platinium/Gold/Silver/Review bands may need recalibration.</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>The null-fallback value (50) was chosen as a neutral midpoint. With real data now flowing, if the actual primitive distributions are skewed (e.g., most stocks have low ROE), the 50-fallback may systematically bias scores upward. Band thresholds (≥75, ≥60, ≥40, &lt;40) were set before any real primitive data was available.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>After backfill completes (post-2026-05-27): run SELECT PERCENTILE_CONT(0.25/0.5/0.75) WITHIN GROUP (ORDER BY quality_score) FROM nidp.v3_stock_scores_daily WHERE score_date = ...; Compare distribution to expected band cutoffs. Adjust if distribution is pathological. (~1 day)</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>Build a calibration pipeline: (a) run v3_scores_engine on a test date with 100% primitive coverage, (b) plot score distribution per primitive and composite, (c) adjust weights or normalization to produce a roughly uniform distribution, (d) version the calibration in a scoring_config table. (~1 week)</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>backend/nidp/services/v3_scores_engine/  •  nidp.v3_stock_scores_daily</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>NIDP Backend</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>Deferred until full Nifty 500 backfill completes. Do not surface scores in V3 UI until calibrated. Track with NIDP-T33 (ranking gate). See scoring_ux_defer_until_v3.md memory.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>NIDP-T33</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>UX / Data Quality</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>v3_scores_engine → Copilot API</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Ranking gate missing — scores shown even when coverage &lt; 50% (misleading)</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Stocks with quality_coverage_pct &lt; 50% still get a score and appear in rankings. A score based on 2/6 primitives (the volatility and dividend defaults) is not meaningful and misleads users into thinking the stock has been properly evaluated.</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>No coverage gate has been implemented in v3_scores_engine or the API serving scores. Stocks with sparse fundamental data (new listings, financials not yet backfilled) get a composite score that is mathematically valid but fundamentally misleading.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>Add a coverage threshold to v3_scores_engine: if quality_coverage_pct &lt; 0.5, set quality_score = NULL and quality_tier = "insufficient_data". Same for health_coverage_pct. API consumers should surface "Insufficient Data" in UI instead of a score. (~1 day)</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>Implement a tiered confidence model: 3 tiers (FULL_COVERAGE ≥80%, PARTIAL 50-80%, INSUFFICIENT &lt;50%). Each tier gets different UI treatment: FULL shows score + rank, PARTIAL shows score with caveat, INSUFFICIENT shows "Not enough data". Document the tier in v3_stock_scores_daily. (~3 days)</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>backend/nidp/services/v3_scores_engine/  •  backend/routes/intelligence.py (score API)  •  nidp.v3_stock_scores_daily (quality_coverage_pct, health_coverage_pct columns)</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>NIDP Backend + Frontend</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>Pairs with NIDP-T32 (calibration). Do not surface in V3 UI until both T32 and T33 are done. Listed in scoring UX honesty backlog — see project_scoring_ux_defer_until_v3.md memory.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>NIDP-T34</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Data Quality</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>v3_scores_engine (earnings_consistency_score)</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>earnings_consistency_score methodology not validated for loss-making companies</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>earnings_consistency_score uses EPS sign-consistency over 5 quarters. A company with consistent losses (always negative EPS) would get a HIGH consistency score, which is counterintuitive — consistent losses should lower quality, not raise it.</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Current implementation counts "consistent" as: variance of EPS sign is low (all positive or all negative). This treats companies that consistently lose money as having high earnings consistency, conflating consistency with positivity.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>Review current implementation in v3_scores_engine. If using EPS sign variance: add a condition that if median EPS &lt; 0 (loss-making), consistency_score should be penalized regardless of sign variance. Also handle NaN EPS gracefully. (~1 day)</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>Replace with a more nuanced metric: (a) compute EPS growth consistency as: % of quarters with positive QoQ EPS growth over 5Q, (b) penalize for loss-making quarters regardless of trend, (c) reward for consistently growing EPS even from a low base. Back-test against known fundamentally strong stocks (HDFC Bank, TCS) to validate. (~3 days)</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>backend/nidp/services/v3_scores_engine/  •  nidp.stock_features_daily (earnings_consistency_score column)</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>NIDP Backend</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>Should be resolved before V3 scores are surfaced in UI (pairs with NIDP-T32, NIDP-T33). earnings_consistency_score is 20% of Quality score — material impact.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>NIDP-T35</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Infrastructure</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>ALL feeds</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Feed registry table not built — no SLA tracking or replay eligibility per feed</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>No feed_registry or feed_execution tables exist. SLA breaches are invisible. Replay eligibility (which raw files can be used to rebuild derived data) is untracked.</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>PRD specifies feed_registry + feed_execution + feed_dependencies tables as Phase 1 foundations. Not prioritized because immediate data coverage gaps took precedence.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>Define minimal feed_registry schema: (feed_id, feed_name, sla_minutes, retry_policy, owner). Populate with current 42 feeds from Feed Inventory sheet. (~2 days)</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>Full implementation: feed_registry + feed_execution + feed_dependencies + quarantine_records. Integrate with job_log (every job_log row gets a feed_execution_id FK). Build Grafana dashboard for SLA tracking. (~1 week)</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>backend/nidp/migrations/ (new migration)  •  backend/nidp/shared/ (feed_registry client)</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>NIDP Backend</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>Phase 1 item from MASTER_FEEDS_INGESTION_IMPROVEMENTS.md roadmap. Prerequisite for replay engine (NIDP-T36). Queue behind coverage fixes.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>NIDP-T36</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Infrastructure</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>ALL derived layers</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Replay engine not built — cannot rebuild derived data from raw archives</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>If nse_financials_quarterly or stock_features_daily becomes corrupt or needs recalculation with a new algorithm, there is no automated way to replay raw files through the pipeline. Manual intervention required for any historical rebuild.</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Architecture calls for a replay engine that reads from MinIO raw archive → re-parses → rebuilds derived tables. Not built yet. MinIO object storage is live but raw files are not systematically archived.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>N/A for immediate short-term (backfill mechanism serves as manual replay for screener data)</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>Implement replay engine: (a) raw file archiving to MinIO (every downloaded file archived immediately), (b) replay_requested Kafka topic, (c) replay worker that reads from MinIO → runs through parsers → upserts into target tables, (d) feed_execution tracking for replay lineage. (~2-3 weeks)</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>backend/nidp/services/replay_engine/ (new)  •  MinIO integration in all ingesters</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>NIDP Backend</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>Phase 1 item from MASTER_FEEDS_INGESTION_IMPROVEMENTS.md roadmap. Depends on NIDP-T35 (feed registry).</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>NIDP-T37</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Infrastructure / HA</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>PostgreSQL on nidp-stack-vm</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>PostgreSQL HA not implemented — single point of failure</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>TimescaleDB (port 5433) is the single source of truth for all NIDP data. No WAL replication, no standby. Any VM failure = complete data platform outage.</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>WAL replication not configured. The PRD calls for streaming replication to a standby PostgreSQL on VM-2, but VM-2 architecture is not yet deployed.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>N/A — VM-2 not provisioned yet</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>Implement PostgreSQL streaming replication: (a) provision VM-2 (16 vCPU / 64 GB / 1 TB NVMe as per PRD specs), (b) configure WAL archiving from VM-1 TimescaleDB to VM-2, (c) set up standby promotion procedure, (d) schedule weekly PITR recovery drill. (~2-3 weeks)</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>Infrastructure (GCP VM provisioning + PostgreSQL replication config)</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>Infrastructure</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>Phase 1 item from MASTER_FEEDS_INGESTION_IMPROVEMENTS.md. Currently single-point-of-failure for the entire platform. Budget impact: additional VM adds ~$150-200/month to infrastructure cost.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>NIDP-T38</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Performance</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>prices_eod + stock_features_daily</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>TimescaleDB continuous aggregates not enabled — rolling averages computed on-the-fly</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SMA20/50/100/200, RSI14, and similar rolling metrics are computed fresh per query. As data volume grows, this creates compounding query latency. </t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Technical indicator engine computes rolling aggregates in Python on every run rather than using materialized TimescaleDB continuous aggregates.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>N/A — not yet causing SLA misses</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>Enable TimescaleDB continuous aggregates for: (a) daily_prices_agg (OHLCV with rolling 20/50/200 day SMAs), (b) rolling_volume_20d, (c) factor_summary_weekly. Add compression policy for chunks &gt; 30 days. (~1 week)</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>backend/nidp/migrations/ (continuous aggregate migration)  •  backend/nidp/services/technical_indicator_engine/ (update to read from aggregates)</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>NIDP Backend</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>Phase 2 item from MASTER_FEEDS_INGESTION_IMPROVEMENTS.md. Defer until data volume actually causes query latency issues. Monitor via Grafana query latency panel.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>NIDP-T39</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Analytics</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>nse_financials_quarterly + stock_features_daily</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>No Parquet export + DuckDB analytics layer — backtesting and AI dataset generation not possible</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>No mechanism to export NIDP data to Parquet files in MinIO for analytics/backtesting. Historical factor research and AI training dataset generation must be done via live PostgreSQL queries, which is slow and contends with production ingestion.</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Phase 2 item from PRD not yet implemented. DuckDB architecture defined but not built. MinIO is live but Parquet archival jobs do not exist.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>N/A — no immediate user-facing impact</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>Implement Parquet export pipeline: (a) weekly export job: nse_financials_quarterly + stock_features_daily → Parquet → MinIO, (b) DuckDB query layer reading from MinIO Parquet files, (c) Jupyter notebook environment for factor research using DuckDB. Estimated data: ~5 GB initial, +100 MB/month incremental. (~2-3 weeks)</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>backend/nidp/services/parquet_exporter/ (new)  •  docs/ (DuckDB query guide)</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>NIDP Backend</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>Phase 2 item from MASTER_FEEDS_INGESTION_IMPROVEMENTS.md. Prerequisite for AI dataset generation (S15 phase). MinIO object storage already live on nidp-stack-vm.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A4:M29"/>
   <mergeCells count="2">
